--- a/archive/2026-04-27/report.xlsx
+++ b/archive/2026-04-27/report.xlsx
@@ -603,7 +603,7 @@
   <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -664,7 +664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>kkr vs lsg</t>
+          <t>아스널 fc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -695,7 +695,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>torino vs inter</t>
+          <t>portland thorns vs angel city fc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -753,7 +753,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Stocks</t>
+          <t>관련주</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -774,17 +774,17 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Ape Wisdom | Trending Stocks on r/wallstreetbets</t>
+          <t>실시간 테마주 순위 | 급상승 테마 관련주 정보 - 알파스퀘어</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fisa</t>
+          <t>manny machado</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lg그룹</t>
+          <t>포틀랜드 대 샌안토니오</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -846,12 +846,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>arthur fils</t>
+          <t>Stocks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -859,25 +859,25 @@
           <t>US</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>92</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>RSS</t>
-        </is>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Ape Wisdom | Trending Stocks on r/wallstreetbets</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>เชลซี พบ ลีดส์</t>
+          <t>guastatoya - marquense</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -908,7 +908,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>chelsea đấu với leeds</t>
+          <t>연금</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>oklahoma city bombing</t>
+          <t>liga nacional de guatemala</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>총정리</t>
+          <t>마라톤</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1010,25 +1010,25 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
       <c r="E13" t="n">
-        <v>86</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>88</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ETFs</t>
+          <t>테마주</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1049,7 +1049,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7 Best Thematic ETFs to Buy in 2026 | Investing | U.S. News</t>
+          <t>실시간 테마주 순위 | 급상승 테마 관련주 정보 - 알파스퀘어</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1059,65 +1059,65 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>캐즘</t>
+          <t>ETFs</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7 Best Thematic ETFs to Buy in 2026 | Investing | U.S. News</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>heavy snow warning</t>
+          <t>캐즘</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>5</v>
-      </c>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="n">
-        <v>84</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>RSS</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>2.84</v>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>킵초게</t>
+          <t>ryan blaney</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1148,12 +1148,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>양극재</t>
+          <t>김서현</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1161,26 +1161,30 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
       <c r="E18" t="n">
-        <v>80</v>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="n">
-        <v>2.69</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>신현지</t>
+          <t>양극재</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1188,25 +1192,21 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>6</v>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="n">
         <v>80</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>RSS</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>2.69</v>
+      </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>emilio nava</t>
+          <t>pete crow armstrong</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>테마주</t>
+          <t>짱구</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1250,25 +1250,25 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>6</v>
+      </c>
       <c r="E21" t="n">
-        <v>78</v>
-      </c>
-      <c r="F21" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>MSCI Korea 테마주 관련주 86종목 정리 - judal.co.kr</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>6</v>
-      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>관련주</t>
+          <t>총정리</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1289,7 +1289,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>MSCI Korea 테마주 관련주 86종목 정리 - judal.co.kr</t>
+          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1299,7 +1299,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>수혜주</t>
+          <t>이재명</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>이차전지</t>
+          <t>수혜주</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1345,24 +1345,28 @@
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>이재명 관련주 - 정책 수혜주 Top 10 총정리 (2025 최신판)</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>의료</t>
+          <t>이차전지</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1370,25 +1374,21 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>7</v>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="n">
-        <v>76</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>RSS</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>2.59</v>
+      </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>carter page</t>
+          <t>kt</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1419,7 +1419,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>쉐보레</t>
+          <t>mariners standings</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1429,14 +1429,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>paris fc vs losc</t>
+          <t>박지윤</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1481,33 +1481,33 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>bragantino vs palmeiras</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
       <c r="E29" t="n">
-        <v>70</v>
-      </c>
-      <c r="F29" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>오늘의 급등주 순위 - 실시간 상승률 Top 종목 | 알파스퀘어 특징종목</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>5</v>
-      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1543,7 +1543,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Trending</t>
+          <t>Thematic</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1564,7 +1564,7 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ape Wisdom | Trending Stocks on r/wallstreetbets</t>
+          <t>PRESS RELEASE: T. Rowe Price Introduces New Thematic ETF Focused On ...</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -1574,7 +1574,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Thematic</t>
+          <t>ETF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ETF</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1626,7 +1626,7 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>PRESS RELEASE: T. Rowe Price Introduces New Thematic ETF Focused On ...</t>
+          <t>Top Trending WallStreetBets Stocks (WSB) in Last 24hrs - LIVE</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -1636,38 +1636,38 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>이재명</t>
+          <t>joey logano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>google</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KR</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
       <c r="E34" t="n">
-        <v>70</v>
-      </c>
-      <c r="F34" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>RSS</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>이재명 관련주 - 정책 수혜주 Top 10 총정리 (2025 최신판)</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>로봇</t>
+          <t>제니</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1698,7 +1698,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dortmund vs sc freiburg</t>
+          <t>김부겸</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1708,14 +1708,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>jannik sinner</t>
+          <t>joao fonseca</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1760,12 +1760,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>돌싱글즈</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>google</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1773,25 +1773,25 @@
           <t>KR</t>
         </is>
       </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>64</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>RSS</t>
-        </is>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>주식 토론은 어디서? 종목토론방 Top 5 소개 : 네이버 블로그</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>quot</t>
+          <t>Trending</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1812,7 +1812,7 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>&amp;quot;오늘 장 급등? Kospi 기술주 강세 배경과 정책 기대감 분석&amp;quot;</t>
+          <t>Ape Wisdom | Trending Stocks on r/wallstreetbets</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -1822,17 +1822,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>wallstreetbets</t>
+          <t>HBM3</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -1840,15 +1840,11 @@
         <v>62</v>
       </c>
       <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>wallstreetbets - Reddit</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>4</v>
-      </c>
+      <c r="G40" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1880,7 +1876,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HBM3</t>
+          <t>전고체</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1895,11 +1891,11 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
@@ -1907,74 +1903,66 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Top</t>
+          <t>배터리 셀</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>WallStreetBets Stocks | Top r/wallstreetbets - TipRanks.com</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>4</v>
-      </c>
+      <c r="G43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WallStreetBets</t>
+          <t>하이브</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>WallStreetBets Stocks | Top r/wallstreetbets - TipRanks.com</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>4</v>
-      </c>
+      <c r="G44" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>블로그</t>
+          <t>원전 수출</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1984,23 +1972,19 @@
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>4</v>
-      </c>
+      <c r="G45" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>네이버</t>
+          <t>wallstreetbets</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2010,33 +1994,33 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
+          <t>wallstreetbets - Reddit</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>전고체</t>
+          <t>블로그</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2046,24 +2030,28 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>배터리 셀</t>
+          <t>실시간</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2073,24 +2061,28 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>오늘 주식 시황 · Kospi Kosdaq 실시간</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>하이브</t>
+          <t>Kospi</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2100,24 +2092,28 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>오늘 주식 시황 · Kospi Kosdaq 실시간</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>원전 수출</t>
+          <t>com</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2127,19 +2123,23 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>코스피 (KS11) - Investing.com</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>Best</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2160,7 +2160,7 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WallStreetBets Stocks | Top r/wallstreetbets - TipRanks.com</t>
+          <t>This Week&amp;#x27;s Best Performing Stocks, Sectors, Industries Rankings ...</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -2170,7 +2170,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Yahoo</t>
+          <t>today</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2191,7 +2191,7 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Visual heatmap of stocks with the highest interest today - Yahoo Finance</t>
+          <t>Top 100 most popular meme stocks today - feargreedmeter.com</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -2201,7 +2201,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>실시간</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
@@ -2222,7 +2222,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>오늘의 급등주 순위 - 실시간 상승률 Top 종목 | 알파스퀘어 특징종목</t>
+          <t>wallstreetbets - Reddit</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -2232,7 +2232,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>com</t>
+          <t>WallStreetBets</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>코스피 (KS11) - Investing.com</t>
+          <t>Top Trending WallStreetBets Stocks (WSB) in Last 24hrs - LIVE</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -2263,7 +2263,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2284,7 +2284,7 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Top Stock Gainers In The Past Week</t>
+          <t>Top 100 most popular meme stocks today - feargreedmeter.com</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -2294,7 +2294,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Kospi</t>
+          <t>네이버</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2315,7 +2315,7 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>오늘 주식 시황 · Kospi Kosdaq 실시간</t>
+          <t>2025년 로봇 테마주 총정리: Kospi·Kosdaq 관련주 흐름과 전망 : 네이버 블로그</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -2325,34 +2325,38 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>전력기기</t>
+          <t>Yahoo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>naver</t>
+          <t>web</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Visual heatmap of stocks with the highest interest today - Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>신한울</t>
+          <t>전력기기</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2367,11 +2371,11 @@
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
@@ -2379,7 +2383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>피규어</t>
+          <t>신한울</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2406,7 +2410,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DRAM</t>
+          <t>피규어</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2421,11 +2425,11 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
@@ -2460,7 +2464,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>르세라핌</t>
+          <t>DRAM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2475,11 +2479,11 @@
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
@@ -2514,7 +2518,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>K드라마</t>
+          <t>르세라핌</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2529,11 +2533,11 @@
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
@@ -2541,12 +2545,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>코스피</t>
+          <t>K드라마</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>naver</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2556,18 +2560,14 @@
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>코스피 (KS11) - Investing.com</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>2</v>
-      </c>
+      <c r="G65" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
